--- a/test/fixtures/demo/monthly-sales/output/월간매출요약_2026-08.xlsx
+++ b/test/fixtures/demo/monthly-sales/output/월간매출요약_2026-08.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="요약" sheetId="1" r:id="rId1"/>
+    <sheet name="카테고리별" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -418,13 +419,13 @@
         <v>2026-08</v>
       </c>
       <c r="B2">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C2">
-        <v>10479300</v>
+        <v>8466900</v>
       </c>
       <c r="D2">
-        <v>58218</v>
+        <v>56825</v>
       </c>
     </row>
   </sheetData>
@@ -432,4 +433,81 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>카테고리</v>
+      </c>
+      <c r="B1" t="str">
+        <v>주문건수</v>
+      </c>
+      <c r="C1" t="str">
+        <v>매출</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>전자기기</v>
+      </c>
+      <c r="B2">
+        <v>38</v>
+      </c>
+      <c r="C2">
+        <v>4036300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>식품</v>
+      </c>
+      <c r="B3">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>2707100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>문구</v>
+      </c>
+      <c r="B4">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>896100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>생활용품</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>827400</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>합계</v>
+      </c>
+      <c r="B6">
+        <v>149</v>
+      </c>
+      <c r="C6">
+        <v>8466900</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
 </file>